--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/22.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/22.xlsx
@@ -426,13 +426,13 @@
         <v>-4.47992836621731</v>
       </c>
       <c r="E2">
-        <v>-26.29021642482813</v>
+        <v>-27.83662689981145</v>
       </c>
       <c r="F2">
-        <v>-5.714206060338529</v>
+        <v>-6.465595351314383</v>
       </c>
       <c r="G2">
-        <v>-17.71891523352043</v>
+        <v>-17.19462852786611</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.605805097223911</v>
       </c>
       <c r="E3">
-        <v>-26.76777117978101</v>
+        <v>-28.60934306211028</v>
       </c>
       <c r="F3">
-        <v>-5.75955586217219</v>
+        <v>-5.90849300772593</v>
       </c>
       <c r="G3">
-        <v>-17.43044664012184</v>
+        <v>-15.67957205050513</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.813227039254987</v>
       </c>
       <c r="E4">
-        <v>-27.21193296740134</v>
+        <v>-27.97747149839801</v>
       </c>
       <c r="F4">
-        <v>-5.694836345358868</v>
+        <v>-6.062030905834819</v>
       </c>
       <c r="G4">
-        <v>-17.22653020447781</v>
+        <v>-17.27236394783092</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.059780167137869</v>
       </c>
       <c r="E5">
-        <v>-27.85821866388002</v>
+        <v>-28.79081712949366</v>
       </c>
       <c r="F5">
-        <v>-5.585167128167436</v>
+        <v>-6.175199146935676</v>
       </c>
       <c r="G5">
-        <v>-17.28372517748049</v>
+        <v>-16.67823972250538</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.316173419667239</v>
       </c>
       <c r="E6">
-        <v>-28.24687947406234</v>
+        <v>-29.33152598295752</v>
       </c>
       <c r="F6">
-        <v>-5.697306536954016</v>
+        <v>-5.800286687367842</v>
       </c>
       <c r="G6">
-        <v>-17.38888176601758</v>
+        <v>-16.41983368103443</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.537690360004831</v>
       </c>
       <c r="E7">
-        <v>-28.81872158632893</v>
+        <v>-30.48256444927916</v>
       </c>
       <c r="F7">
-        <v>-5.656008280087446</v>
+        <v>-6.041554492005018</v>
       </c>
       <c r="G7">
-        <v>-17.41446709112735</v>
+        <v>-16.35834851084278</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.686311971157192</v>
       </c>
       <c r="E8">
-        <v>-29.17382640411441</v>
+        <v>-31.0134057578803</v>
       </c>
       <c r="F8">
-        <v>-5.303169326702011</v>
+        <v>-5.625047220040412</v>
       </c>
       <c r="G8">
-        <v>-16.97111007462596</v>
+        <v>-17.33635597129399</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.719502485039093</v>
       </c>
       <c r="E9">
-        <v>-29.73233216042841</v>
+        <v>-30.27260628038753</v>
       </c>
       <c r="F9">
-        <v>-5.233646107319855</v>
+        <v>-5.548868068576761</v>
       </c>
       <c r="G9">
-        <v>-17.02528796440473</v>
+        <v>-17.30647716777369</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.609628894361046</v>
       </c>
       <c r="E10">
-        <v>-30.64256449291817</v>
+        <v>-31.7016794653581</v>
       </c>
       <c r="F10">
-        <v>-5.348499247718006</v>
+        <v>-5.537905454368112</v>
       </c>
       <c r="G10">
-        <v>-16.72687398845947</v>
+        <v>-18.44780743134626</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.333659583470755</v>
       </c>
       <c r="E11">
-        <v>-31.05197250676662</v>
+        <v>-32.12142598536607</v>
       </c>
       <c r="F11">
-        <v>-5.304110352071591</v>
+        <v>-5.205039267431576</v>
       </c>
       <c r="G11">
-        <v>-16.35701797550042</v>
+        <v>-17.4186867420528</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.89140973313203</v>
       </c>
       <c r="E12">
-        <v>-31.05553415157366</v>
+        <v>-32.22506464150561</v>
       </c>
       <c r="F12">
-        <v>-5.309672010813987</v>
+        <v>-5.136660851800088</v>
       </c>
       <c r="G12">
-        <v>-16.37456102656799</v>
+        <v>-16.88635940296706</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.292893739655947</v>
       </c>
       <c r="E13">
-        <v>-31.55997672094708</v>
+        <v>-33.42740392562315</v>
       </c>
       <c r="F13">
-        <v>-5.332200290700523</v>
+        <v>-5.282808884308602</v>
       </c>
       <c r="G13">
-        <v>-15.82111574552567</v>
+        <v>-17.33100593954131</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.575498444288357</v>
       </c>
       <c r="E14">
-        <v>-32.62182236321365</v>
+        <v>-33.97120346259723</v>
       </c>
       <c r="F14">
-        <v>-5.096152029068387</v>
+        <v>-4.945558977076451</v>
       </c>
       <c r="G14">
-        <v>-15.50716682610722</v>
+        <v>-14.72879544777575</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.784550407811609</v>
       </c>
       <c r="E15">
-        <v>-33.05038582211455</v>
+        <v>-34.11528818433629</v>
       </c>
       <c r="F15">
-        <v>-5.026242790476525</v>
+        <v>-5.14766571274628</v>
       </c>
       <c r="G15">
-        <v>-14.82201659289035</v>
+        <v>-15.07666563567574</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.983451790957681</v>
       </c>
       <c r="E16">
-        <v>-33.63644507852822</v>
+        <v>-34.2207382300789</v>
       </c>
       <c r="F16">
-        <v>-4.956263969022829</v>
+        <v>-4.685058138081076</v>
       </c>
       <c r="G16">
-        <v>-14.62861483173356</v>
+        <v>-15.34309754508109</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.227441705476746</v>
       </c>
       <c r="E17">
-        <v>-34.42051865363829</v>
+        <v>-35.69445084758008</v>
       </c>
       <c r="F17">
-        <v>-4.759926812313498</v>
+        <v>-4.623406894127723</v>
       </c>
       <c r="G17">
-        <v>-14.44491072089571</v>
+        <v>-15.40539317699793</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.5707161011119748</v>
       </c>
       <c r="E18">
-        <v>-35.24398315990408</v>
+        <v>-36.87825055911021</v>
       </c>
       <c r="F18">
-        <v>-4.765941588025226</v>
+        <v>-4.577900530854932</v>
       </c>
       <c r="G18">
-        <v>-13.89373440456175</v>
+        <v>-14.55025762028324</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.04435658285318409</v>
       </c>
       <c r="E19">
-        <v>-35.89358369935638</v>
+        <v>-37.34274066655097</v>
       </c>
       <c r="F19">
-        <v>-4.570764145679814</v>
+        <v>-4.634457315281068</v>
       </c>
       <c r="G19">
-        <v>-13.5257552503347</v>
+        <v>-13.88710633701167</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.3306763594923215</v>
       </c>
       <c r="E20">
-        <v>-36.16722806245487</v>
+        <v>-36.31662921267893</v>
       </c>
       <c r="F20">
-        <v>-4.512804106873336</v>
+        <v>-3.800048629012946</v>
       </c>
       <c r="G20">
-        <v>-13.64403016266644</v>
+        <v>-13.67434208743259</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.5567787576961921</v>
       </c>
       <c r="E21">
-        <v>-36.84244165089456</v>
+        <v>-38.21851584031636</v>
       </c>
       <c r="F21">
-        <v>-4.161938324641369</v>
+        <v>-3.909377387201827</v>
       </c>
       <c r="G21">
-        <v>-13.29807456754639</v>
+        <v>-14.53448478824699</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.6436073269645568</v>
       </c>
       <c r="E22">
-        <v>-37.5050570246449</v>
+        <v>-37.60446835029828</v>
       </c>
       <c r="F22">
-        <v>-4.161510058694121</v>
+        <v>-4.217747093302777</v>
       </c>
       <c r="G22">
-        <v>-13.11046744366358</v>
+        <v>-13.26886841444577</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.6148667801376088</v>
       </c>
       <c r="E23">
-        <v>-37.43032588233331</v>
+        <v>-38.31559500185579</v>
       </c>
       <c r="F23">
-        <v>-4.079249033759116</v>
+        <v>-3.147694388695085</v>
       </c>
       <c r="G23">
-        <v>-12.93251367360865</v>
+        <v>-13.82782450709718</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.494978170991156</v>
       </c>
       <c r="E24">
-        <v>-38.22767920747088</v>
+        <v>-39.33254988128432</v>
       </c>
       <c r="F24">
-        <v>-3.850170655454135</v>
+        <v>-3.983703480785416</v>
       </c>
       <c r="G24">
-        <v>-12.6431689940537</v>
+        <v>-13.43243730918409</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.3121338819694904</v>
       </c>
       <c r="E25">
-        <v>-38.05413902654894</v>
+        <v>-39.65367076587923</v>
       </c>
       <c r="F25">
-        <v>-3.852244887430746</v>
+        <v>-3.494865652310566</v>
       </c>
       <c r="G25">
-        <v>-12.83460202227482</v>
+        <v>-13.62903169891822</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.09157122039462107</v>
       </c>
       <c r="E26">
-        <v>-38.3601732999873</v>
+        <v>-40.29983872203372</v>
       </c>
       <c r="F26">
-        <v>-3.70027011861094</v>
+        <v>-3.358202426564106</v>
       </c>
       <c r="G26">
-        <v>-13.05370231068519</v>
+        <v>-13.42211130493652</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.1436584143414439</v>
       </c>
       <c r="E27">
-        <v>-38.16975323220176</v>
+        <v>-39.51700594880175</v>
       </c>
       <c r="F27">
-        <v>-3.74973856317132</v>
+        <v>-3.731555070312468</v>
       </c>
       <c r="G27">
-        <v>-13.14823430381279</v>
+        <v>-13.31441833213398</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.3744842573515481</v>
       </c>
       <c r="E28">
-        <v>-38.66813217487892</v>
+        <v>-40.66429257440803</v>
       </c>
       <c r="F28">
-        <v>-3.61051568215021</v>
+        <v>-3.483963508922322</v>
       </c>
       <c r="G28">
-        <v>-13.44085036126251</v>
+        <v>-13.40412036712608</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.586972888411446</v>
       </c>
       <c r="E29">
-        <v>-38.43534370427762</v>
+        <v>-39.79338098172688</v>
       </c>
       <c r="F29">
-        <v>-3.833648867605299</v>
+        <v>-2.845525840971492</v>
       </c>
       <c r="G29">
-        <v>-13.23068155793695</v>
+        <v>-13.26256518783008</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.7705371297101158</v>
       </c>
       <c r="E30">
-        <v>-38.62222250538916</v>
+        <v>-40.90675386548971</v>
       </c>
       <c r="F30">
-        <v>-3.895234670533831</v>
+        <v>-3.538774094863356</v>
       </c>
       <c r="G30">
-        <v>-13.05965444659402</v>
+        <v>-13.42644907983811</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.9184575990640538</v>
       </c>
       <c r="E31">
-        <v>-38.33965704849555</v>
+        <v>-40.57495483918471</v>
       </c>
       <c r="F31">
-        <v>-3.747384343012564</v>
+        <v>-3.707997958111656</v>
       </c>
       <c r="G31">
-        <v>-13.42537612038817</v>
+        <v>-14.7697057181789</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.025728044288299</v>
       </c>
       <c r="E32">
-        <v>-37.67064067673537</v>
+        <v>-40.41324756084481</v>
       </c>
       <c r="F32">
-        <v>-3.65387326038014</v>
+        <v>-3.751671972689455</v>
       </c>
       <c r="G32">
-        <v>-13.03064844800853</v>
+        <v>-12.86314864984199</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.089905058486826</v>
       </c>
       <c r="E33">
-        <v>-37.65588011570736</v>
+        <v>-40.60825950127412</v>
       </c>
       <c r="F33">
-        <v>-3.655540763961975</v>
+        <v>-3.364991725797451</v>
       </c>
       <c r="G33">
-        <v>-13.49623409996438</v>
+        <v>-13.40584628966635</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.109249054278914</v>
       </c>
       <c r="E34">
-        <v>-37.43047079350156</v>
+        <v>-38.46590411111838</v>
       </c>
       <c r="F34">
-        <v>-3.699312525893304</v>
+        <v>-3.882763599284685</v>
       </c>
       <c r="G34">
-        <v>-13.44164113565833</v>
+        <v>-13.83211306367537</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.083887062634882</v>
       </c>
       <c r="E35">
-        <v>-37.23271006934959</v>
+        <v>-38.5803907267433</v>
       </c>
       <c r="F35">
-        <v>-3.537794964593247</v>
+        <v>-3.593243393434438</v>
       </c>
       <c r="G35">
-        <v>-13.42054288103111</v>
+        <v>-14.490713292644</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.015619207889299</v>
       </c>
       <c r="E36">
-        <v>-37.04116920424716</v>
+        <v>-37.67799944699783</v>
       </c>
       <c r="F36">
-        <v>-3.526573899754926</v>
+        <v>-3.345310544674338</v>
       </c>
       <c r="G36">
-        <v>-13.8330088371611</v>
+        <v>-14.02133290795465</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.9085622034816717</v>
       </c>
       <c r="E37">
-        <v>-36.2374986578689</v>
+        <v>-38.9960797340404</v>
       </c>
       <c r="F37">
-        <v>-3.46982493409134</v>
+        <v>-3.387936674487595</v>
       </c>
       <c r="G37">
-        <v>-13.60431097568937</v>
+        <v>-13.5809585218508</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.7697227149244169</v>
       </c>
       <c r="E38">
-        <v>-36.29584804545773</v>
+        <v>-37.50326148470086</v>
       </c>
       <c r="F38">
-        <v>-3.313800277039247</v>
+        <v>-3.421126042848159</v>
       </c>
       <c r="G38">
-        <v>-13.35593562852564</v>
+        <v>-13.89430533711309</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.6091750044768578</v>
       </c>
       <c r="E39">
-        <v>-35.36848449579696</v>
+        <v>-36.58526961199895</v>
       </c>
       <c r="F39">
-        <v>-3.525284960076169</v>
+        <v>-3.093939971192619</v>
       </c>
       <c r="G39">
-        <v>-13.49347787385444</v>
+        <v>-14.38421140326754</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.4396199899266345</v>
       </c>
       <c r="E40">
-        <v>-35.09316233307862</v>
+        <v>-36.36227849491326</v>
       </c>
       <c r="F40">
-        <v>-3.485728759857687</v>
+        <v>-3.478492970594234</v>
       </c>
       <c r="G40">
-        <v>-13.8259213985927</v>
+        <v>-13.89368026440602</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.2758897316483964</v>
       </c>
       <c r="E41">
-        <v>-34.67178556242789</v>
+        <v>-36.90143634602948</v>
       </c>
       <c r="F41">
-        <v>-3.372965590416799</v>
+        <v>-3.31314421005623</v>
       </c>
       <c r="G41">
-        <v>-13.84575310169799</v>
+        <v>-14.21163063351621</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.1323905966261051</v>
       </c>
       <c r="E42">
-        <v>-34.37078242361204</v>
+        <v>-35.49688937628445</v>
       </c>
       <c r="F42">
-        <v>-3.361322058203049</v>
+        <v>-3.38040184459173</v>
       </c>
       <c r="G42">
-        <v>-14.23236467255034</v>
+        <v>-14.00469547403749</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.02268558731213939</v>
       </c>
       <c r="E43">
-        <v>-33.54905005865419</v>
+        <v>-35.54798188427599</v>
       </c>
       <c r="F43">
-        <v>-3.577343709505104</v>
+        <v>-3.266568424466425</v>
       </c>
       <c r="G43">
-        <v>-13.5086108676866</v>
+        <v>-14.30826096783107</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.04412331192407522</v>
       </c>
       <c r="E44">
-        <v>-32.93563655499718</v>
+        <v>-33.70653227074493</v>
       </c>
       <c r="F44">
-        <v>-3.273939237616535</v>
+        <v>-3.320584606068175</v>
       </c>
       <c r="G44">
-        <v>-13.72200839302665</v>
+        <v>-14.56570561138511</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.06233559382876021</v>
       </c>
       <c r="E45">
-        <v>-33.07128472965994</v>
+        <v>-34.60223273014407</v>
       </c>
       <c r="F45">
-        <v>-3.57763529483089</v>
+        <v>-3.649608824990528</v>
       </c>
       <c r="G45">
-        <v>-14.18348595559007</v>
+        <v>-14.46337087338915</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.03174733818207438</v>
       </c>
       <c r="E46">
-        <v>-31.96344337689748</v>
+        <v>-33.2870438737554</v>
       </c>
       <c r="F46">
-        <v>-3.323427562994583</v>
+        <v>-3.304380911302014</v>
       </c>
       <c r="G46">
-        <v>-13.65628880641253</v>
+        <v>-14.81712757276678</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.04458476900829566</v>
       </c>
       <c r="E47">
-        <v>-32.0272767465096</v>
+        <v>-33.92206951961401</v>
       </c>
       <c r="F47">
-        <v>-3.385454885748807</v>
+        <v>-3.478888930212772</v>
       </c>
       <c r="G47">
-        <v>-14.04127453198218</v>
+        <v>-14.66745629194349</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.1592372149531772</v>
       </c>
       <c r="E48">
-        <v>-31.55952613778332</v>
+        <v>-33.35425095650324</v>
       </c>
       <c r="F48">
-        <v>-3.494250175330286</v>
+        <v>-2.974902747042928</v>
       </c>
       <c r="G48">
-        <v>-14.41274326533769</v>
+        <v>-13.74361687760637</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.3025495460034621</v>
       </c>
       <c r="E49">
-        <v>-30.59819450459101</v>
+        <v>-31.77325199704933</v>
       </c>
       <c r="F49">
-        <v>-3.468222043166923</v>
+        <v>-2.941100386804291</v>
       </c>
       <c r="G49">
-        <v>-14.11502490836304</v>
+        <v>-14.41773564394039</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.4626431533281413</v>
       </c>
       <c r="E50">
-        <v>-29.85804712735534</v>
+        <v>-30.22843328067971</v>
       </c>
       <c r="F50">
-        <v>-3.298756296637005</v>
+        <v>-3.171422144580874</v>
       </c>
       <c r="G50">
-        <v>-13.86863962207511</v>
+        <v>-14.66754324431481</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.6264537272896041</v>
       </c>
       <c r="E51">
-        <v>-29.77745840391484</v>
+        <v>-31.53202697937174</v>
       </c>
       <c r="F51">
-        <v>-3.472159273432429</v>
+        <v>-3.378823804689397</v>
       </c>
       <c r="G51">
-        <v>-14.54187738042042</v>
+        <v>-15.12946213117798</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.7816680773860516</v>
       </c>
       <c r="E52">
-        <v>-29.59687418167397</v>
+        <v>-30.2633817788339</v>
       </c>
       <c r="F52">
-        <v>-3.345634436328832</v>
+        <v>-2.91012855798102</v>
       </c>
       <c r="G52">
-        <v>-14.71016795298278</v>
+        <v>-14.79165052796847</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.9173864487868097</v>
       </c>
       <c r="E53">
-        <v>-28.77191980745966</v>
+        <v>-30.81071126129697</v>
       </c>
       <c r="F53">
-        <v>-3.358416145354028</v>
+        <v>-3.645345217968318</v>
       </c>
       <c r="G53">
-        <v>-14.42466558387394</v>
+        <v>-15.14150913613348</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.027724932043466</v>
       </c>
       <c r="E54">
-        <v>-28.21431974594719</v>
+        <v>-29.82129176807209</v>
       </c>
       <c r="F54">
-        <v>-3.420361459735376</v>
+        <v>-3.349814378243359</v>
       </c>
       <c r="G54">
-        <v>-14.83347461857593</v>
+        <v>-14.36715561360155</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.108508188664997</v>
       </c>
       <c r="E55">
-        <v>-28.34091776530562</v>
+        <v>-29.42011651996958</v>
       </c>
       <c r="F55">
-        <v>-3.563636714090981</v>
+        <v>-3.377912600546318</v>
       </c>
       <c r="G55">
-        <v>-14.76864916483676</v>
+        <v>-15.13991118123403</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.161717338636837</v>
       </c>
       <c r="E56">
-        <v>-27.76107836794149</v>
+        <v>-29.57360008951155</v>
       </c>
       <c r="F56">
-        <v>-3.537055232502547</v>
+        <v>-3.440822134584523</v>
       </c>
       <c r="G56">
-        <v>-14.84664544191554</v>
+        <v>-14.68267787875775</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.19001030150758</v>
       </c>
       <c r="E57">
-        <v>-27.76947868722571</v>
+        <v>-28.766811688779</v>
       </c>
       <c r="F57">
-        <v>-3.424211711423588</v>
+        <v>-3.087631125052898</v>
       </c>
       <c r="G57">
-        <v>-15.09199714341224</v>
+        <v>-15.54152777827773</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.201666234459559</v>
       </c>
       <c r="E58">
-        <v>-26.65138939778389</v>
+        <v>-27.23299037153701</v>
       </c>
       <c r="F58">
-        <v>-3.498232137435543</v>
+        <v>-3.211555716879107</v>
       </c>
       <c r="G58">
-        <v>-15.07549423957902</v>
+        <v>-15.3490677277085</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.204346920965846</v>
       </c>
       <c r="E59">
-        <v>-26.83928484131015</v>
+        <v>-27.49313308938164</v>
       </c>
       <c r="F59">
-        <v>-3.648326512250994</v>
+        <v>-3.154921065917108</v>
       </c>
       <c r="G59">
-        <v>-15.05808899981694</v>
+        <v>-15.0667333780153</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.209415278342671</v>
       </c>
       <c r="E60">
-        <v>-26.23641815361701</v>
+        <v>-26.02110732844831</v>
       </c>
       <c r="F60">
-        <v>-3.420192472785204</v>
+        <v>-3.272190554029225</v>
       </c>
       <c r="G60">
-        <v>-15.2767364796521</v>
+        <v>-15.34664454558685</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.224939551405328</v>
       </c>
       <c r="E61">
-        <v>-26.20717326847547</v>
+        <v>-27.42028805649425</v>
       </c>
       <c r="F61">
-        <v>-3.787309166725292</v>
+        <v>-3.606236336147348</v>
       </c>
       <c r="G61">
-        <v>-15.52769414818311</v>
+        <v>-15.29624006060144</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.260349264116936</v>
       </c>
       <c r="E62">
-        <v>-25.70301372872752</v>
+        <v>-26.46943531215569</v>
       </c>
       <c r="F62">
-        <v>-3.800380804341469</v>
+        <v>-3.358237217995024</v>
       </c>
       <c r="G62">
-        <v>-15.62897561405849</v>
+        <v>-15.97057046572604</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.318555244041693</v>
       </c>
       <c r="E63">
-        <v>-25.94101673714865</v>
+        <v>-25.95678035516935</v>
       </c>
       <c r="F63">
-        <v>-3.786054190110051</v>
+        <v>-3.55800547248675</v>
       </c>
       <c r="G63">
-        <v>-15.67482412290861</v>
+        <v>-16.2380293974795</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.401124803036447</v>
       </c>
       <c r="E64">
-        <v>-25.31019577940616</v>
+        <v>-26.26800425982051</v>
       </c>
       <c r="F64">
-        <v>-3.626306849949778</v>
+        <v>-3.335781834439935</v>
       </c>
       <c r="G64">
-        <v>-16.29796747170587</v>
+        <v>-16.30095994576809</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.50448314489238</v>
       </c>
       <c r="E65">
-        <v>-25.23121919271239</v>
+        <v>-25.29579523206177</v>
       </c>
       <c r="F65">
-        <v>-3.80709803561077</v>
+        <v>-3.657426128170747</v>
       </c>
       <c r="G65">
-        <v>-15.89921702169436</v>
+        <v>-16.60724557223445</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.623715826607156</v>
       </c>
       <c r="E66">
-        <v>-25.49176947321772</v>
+        <v>-25.21734394835289</v>
       </c>
       <c r="F66">
-        <v>-4.040419311752889</v>
+        <v>-3.512562065136572</v>
       </c>
       <c r="G66">
-        <v>-16.26583775019579</v>
+        <v>-17.29418571181201</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.749560543754707</v>
       </c>
       <c r="E67">
-        <v>-25.0241773610817</v>
+        <v>-24.99582911379369</v>
       </c>
       <c r="F67">
-        <v>-4.062981554702939</v>
+        <v>-4.266653076396657</v>
       </c>
       <c r="G67">
-        <v>-15.95181828451381</v>
+        <v>-16.65016559084277</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.871120895252343</v>
       </c>
       <c r="E68">
-        <v>-24.8942871411197</v>
+        <v>-25.26126108927928</v>
       </c>
       <c r="F68">
-        <v>-3.972035925916985</v>
+        <v>-3.511253244640149</v>
       </c>
       <c r="G68">
-        <v>-16.15349528644352</v>
+        <v>-16.33632823295734</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.975229010184499</v>
       </c>
       <c r="E69">
-        <v>-24.1172236437735</v>
+        <v>-24.68215530470439</v>
       </c>
       <c r="F69">
-        <v>-4.096987693322665</v>
+        <v>-3.913882049138251</v>
       </c>
       <c r="G69">
-        <v>-16.09941583331154</v>
+        <v>-16.01601702493513</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.049238113294938</v>
       </c>
       <c r="E70">
-        <v>-24.27936112714413</v>
+        <v>-24.53697242801848</v>
       </c>
       <c r="F70">
-        <v>-4.108877250655047</v>
+        <v>-4.108714062276695</v>
       </c>
       <c r="G70">
-        <v>-15.90782858767712</v>
+        <v>-15.04522333008236</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.081252144637092</v>
       </c>
       <c r="E71">
-        <v>-24.33078647797523</v>
+        <v>-24.28484963764143</v>
       </c>
       <c r="F71">
-        <v>-4.183173523012134</v>
+        <v>-4.238379240204305</v>
       </c>
       <c r="G71">
-        <v>-16.1314503993964</v>
+        <v>-16.00319893291316</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.062663501272143</v>
       </c>
       <c r="E72">
-        <v>-24.50848832651023</v>
+        <v>-24.48791546909338</v>
       </c>
       <c r="F72">
-        <v>-4.221257714355842</v>
+        <v>-4.394914999943924</v>
       </c>
       <c r="G72">
-        <v>-15.96649846977077</v>
+        <v>-16.54303862875924</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.988384082841391</v>
       </c>
       <c r="E73">
-        <v>-24.32078307889229</v>
+        <v>-24.71655359326665</v>
       </c>
       <c r="F73">
-        <v>-4.24109711365289</v>
+        <v>-4.347991300044943</v>
       </c>
       <c r="G73">
-        <v>-15.52899023069909</v>
+        <v>-15.77101313292373</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.860247598643012</v>
       </c>
       <c r="E74">
-        <v>-24.79041300433175</v>
+        <v>-25.12432003528733</v>
       </c>
       <c r="F74">
-        <v>-4.324793699296946</v>
+        <v>-4.337229979115174</v>
       </c>
       <c r="G74">
-        <v>-15.78427747107779</v>
+        <v>-15.53260121502526</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.684102586275926</v>
       </c>
       <c r="E75">
-        <v>-25.006049879629</v>
+        <v>-24.59836947861447</v>
       </c>
       <c r="F75">
-        <v>-4.425861977745111</v>
+        <v>-4.538418883702702</v>
       </c>
       <c r="G75">
-        <v>-15.83311025093622</v>
+        <v>-16.21169267263262</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.470639551114411</v>
       </c>
       <c r="E76">
-        <v>-25.12562423580154</v>
+        <v>-24.36291600105966</v>
       </c>
       <c r="F76">
-        <v>-4.390218156770051</v>
+        <v>-5.153267961491412</v>
       </c>
       <c r="G76">
-        <v>-15.51208701783561</v>
+        <v>-16.11067042326043</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.231796390588416</v>
       </c>
       <c r="E77">
-        <v>-25.12597292830013</v>
+        <v>-25.70596176530652</v>
       </c>
       <c r="F77">
-        <v>-4.447688630441474</v>
+        <v>-4.793894017665292</v>
       </c>
       <c r="G77">
-        <v>-15.06892851523857</v>
+        <v>-15.14035742736612</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.9833460117719001</v>
       </c>
       <c r="E78">
-        <v>-25.45397030067569</v>
+        <v>-25.61628892300663</v>
       </c>
       <c r="F78">
-        <v>-4.505722393946803</v>
+        <v>-4.803530415662059</v>
       </c>
       <c r="G78">
-        <v>-14.99896138731575</v>
+        <v>-14.86240022723322</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.7394283283953276</v>
       </c>
       <c r="E79">
-        <v>-25.77415605538802</v>
+        <v>-27.2509955841915</v>
       </c>
       <c r="F79">
-        <v>-4.526894636394955</v>
+        <v>-4.824081382558111</v>
       </c>
       <c r="G79">
-        <v>-14.85144094722467</v>
+        <v>-15.0655439352</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.5161488226128981</v>
       </c>
       <c r="E80">
-        <v>-26.37992096644607</v>
+        <v>-26.62727074521904</v>
       </c>
       <c r="F80">
-        <v>-4.582667785258043</v>
+        <v>-5.039945644053635</v>
       </c>
       <c r="G80">
-        <v>-14.69184233057328</v>
+        <v>-14.84646989656211</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.3250792764921142</v>
       </c>
       <c r="E81">
-        <v>-26.82061847145053</v>
+        <v>-26.97251254661581</v>
       </c>
       <c r="F81">
-        <v>-4.657326882537557</v>
+        <v>-4.67680677038179</v>
       </c>
       <c r="G81">
-        <v>-14.86574871383463</v>
+        <v>-15.04105453809108</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.1778899008341024</v>
       </c>
       <c r="E82">
-        <v>-26.89751196010077</v>
+        <v>-26.56474157612112</v>
       </c>
       <c r="F82">
-        <v>-4.58408429351683</v>
+        <v>-4.75910175838031</v>
       </c>
       <c r="G82">
-        <v>-14.1939694584725</v>
+        <v>-14.65821637203209</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.0810038599705433</v>
       </c>
       <c r="E83">
-        <v>-27.99422685222639</v>
+        <v>-26.59125126296203</v>
       </c>
       <c r="F83">
-        <v>-4.773841727945724</v>
+        <v>-4.856634564753326</v>
       </c>
       <c r="G83">
-        <v>-13.713775808134</v>
+        <v>-14.06059436452419</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.03966167494632439</v>
       </c>
       <c r="E84">
-        <v>-28.25351368848358</v>
+        <v>-28.06588089644976</v>
       </c>
       <c r="F84">
-        <v>-4.800543322807563</v>
+        <v>-4.563753672349922</v>
       </c>
       <c r="G84">
-        <v>-13.90698889905112</v>
+        <v>-14.12912103618241</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.05510245184744128</v>
       </c>
       <c r="E85">
-        <v>-29.45964330534553</v>
+        <v>-27.78916396373706</v>
       </c>
       <c r="F85">
-        <v>-4.826564828031704</v>
+        <v>-5.580942454413158</v>
       </c>
       <c r="G85">
-        <v>-13.30595934295374</v>
+        <v>-13.96989811939958</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.1261113606709557</v>
       </c>
       <c r="E86">
-        <v>-29.77175026242817</v>
+        <v>-30.16129186080498</v>
       </c>
       <c r="F86">
-        <v>-4.936552138305812</v>
+        <v>-5.213987292116617</v>
       </c>
       <c r="G86">
-        <v>-13.38733691884952</v>
+        <v>-13.67174007873595</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.2499955738434198</v>
       </c>
       <c r="E87">
-        <v>-30.39212176639796</v>
+        <v>-31.88998247154505</v>
       </c>
       <c r="F87">
-        <v>-4.923264296797504</v>
+        <v>-5.20514695519394</v>
       </c>
       <c r="G87">
-        <v>-13.10317000691537</v>
+        <v>-13.30361655076029</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.4212948167370626</v>
       </c>
       <c r="E88">
-        <v>-31.81334257743924</v>
+        <v>-32.11903947956403</v>
       </c>
       <c r="F88">
-        <v>-4.936327650739653</v>
+        <v>-5.122104779798095</v>
       </c>
       <c r="G88">
-        <v>-13.18623413069272</v>
+        <v>-13.89351784393882</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.6364918638798693</v>
       </c>
       <c r="E89">
-        <v>-32.9284974157241</v>
+        <v>-33.48865380081389</v>
       </c>
       <c r="F89">
-        <v>-5.069520017068383</v>
+        <v>-5.290838249543937</v>
       </c>
       <c r="G89">
-        <v>-13.35809795353331</v>
+        <v>-12.83780121329528</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.8877130255406619</v>
       </c>
       <c r="E90">
-        <v>-34.33815250414978</v>
+        <v>-34.55953148448875</v>
       </c>
       <c r="F90">
-        <v>-5.170446644690669</v>
+        <v>-5.142229137481706</v>
       </c>
       <c r="G90">
-        <v>-12.84766784652453</v>
+        <v>-13.01736278191433</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.17109600586612</v>
       </c>
       <c r="E91">
-        <v>-34.8865778773227</v>
+        <v>-36.46988635852052</v>
       </c>
       <c r="F91">
-        <v>-5.254100155229779</v>
+        <v>-5.587136985851293</v>
       </c>
       <c r="G91">
-        <v>-12.53465899708286</v>
+        <v>-12.79597548207704</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.476335890029761</v>
       </c>
       <c r="E92">
-        <v>-36.33867835262228</v>
+        <v>-36.20351925315234</v>
       </c>
       <c r="F92">
-        <v>-5.274642838451805</v>
+        <v>-5.655177427582439</v>
       </c>
       <c r="G92">
-        <v>-13.01667044416529</v>
+        <v>-13.34161309641866</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.799321444671308</v>
       </c>
       <c r="E93">
-        <v>-38.14561420150388</v>
+        <v>-37.45449208387525</v>
       </c>
       <c r="F93">
-        <v>-5.183922525599411</v>
+        <v>-6.362425918949017</v>
       </c>
       <c r="G93">
-        <v>-13.01337937894117</v>
+        <v>-12.9673405592406</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.128963603750853</v>
       </c>
       <c r="E94">
-        <v>-39.42630967137612</v>
+        <v>-39.18020748719228</v>
       </c>
       <c r="F94">
-        <v>-5.406098946704266</v>
+        <v>-6.052141027412795</v>
       </c>
       <c r="G94">
-        <v>-13.20031385240429</v>
+        <v>-13.0080933310089</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.461427877705417</v>
       </c>
       <c r="E95">
-        <v>-40.92155971125779</v>
+        <v>-40.43004140670225</v>
       </c>
       <c r="F95">
-        <v>-5.411650665037829</v>
+        <v>-5.796355255674156</v>
       </c>
       <c r="G95">
-        <v>-13.77339724447989</v>
+        <v>-13.61193653459351</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.787109877759772</v>
       </c>
       <c r="E96">
-        <v>-42.68996956751914</v>
+        <v>-42.44202882288817</v>
       </c>
       <c r="F96">
-        <v>-5.568339672746967</v>
+        <v>-6.39091885831941</v>
       </c>
       <c r="G96">
-        <v>-13.78343614184101</v>
+        <v>-13.4664504518693</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.101517370346579</v>
       </c>
       <c r="E97">
-        <v>-44.16689287309175</v>
+        <v>-43.91442139021612</v>
       </c>
       <c r="F97">
-        <v>-5.670083070628413</v>
+        <v>-5.823813978342153</v>
       </c>
       <c r="G97">
-        <v>-13.83172916075292</v>
+        <v>-13.64256345662937</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.395824343430641</v>
       </c>
       <c r="E98">
-        <v>-45.88113085903635</v>
+        <v>-46.45677236099537</v>
       </c>
       <c r="F98">
-        <v>-5.651862301236435</v>
+        <v>-5.928431811111315</v>
       </c>
       <c r="G98">
-        <v>-13.98108708491728</v>
+        <v>-14.17956653643731</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.662472523432102</v>
       </c>
       <c r="E99">
-        <v>-47.52565298763285</v>
+        <v>-48.18457086235593</v>
       </c>
       <c r="F99">
-        <v>-5.752351550870043</v>
+        <v>-6.251600715046979</v>
       </c>
       <c r="G99">
-        <v>-14.07121731932289</v>
+        <v>-14.24198029233029</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.892174431516966</v>
       </c>
       <c r="E100">
-        <v>-49.70289574154367</v>
+        <v>-49.06975394087225</v>
       </c>
       <c r="F100">
-        <v>-5.824553710432854</v>
+        <v>-6.105004949957252</v>
       </c>
       <c r="G100">
-        <v>-14.75438733532864</v>
+        <v>-14.79365699495207</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.071057159325806</v>
       </c>
       <c r="E101">
-        <v>-50.94333873808024</v>
+        <v>-51.23428753248055</v>
       </c>
       <c r="F101">
-        <v>-5.788677118217607</v>
+        <v>-6.325751194741174</v>
       </c>
       <c r="G101">
-        <v>-14.58870369329525</v>
+        <v>-15.12923572689038</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.19180111411326</v>
       </c>
       <c r="E102">
-        <v>-52.82343434879276</v>
+        <v>-51.97627120592633</v>
       </c>
       <c r="F102">
-        <v>-6.129979398784253</v>
+        <v>-6.285822643375133</v>
       </c>
       <c r="G102">
-        <v>-14.51110444402517</v>
+        <v>-14.66128103296861</v>
       </c>
     </row>
   </sheetData>
